--- a/table/tier.xlsx
+++ b/table/tier.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/051929d70086d0fa/fudan/projects/findme/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{9C1FEFB7-E2F9-4100-8630-65FEB9F93E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{848C51A8-A8DA-41B1-9E10-0FEFC06620D9}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{9C1FEFB7-E2F9-4100-8630-65FEB9F93E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B846440-6563-419F-8980-8D8CB1BFDBAD}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tier1" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">tier1!$O$1:$AL$372</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">tier2!$A$1:$AJ$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">tier3!$A$1:$AJ$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">tier4!$A$1:$AJ$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">tier5!$A$1:$AJ$219</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -53183,6 +53186,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37091296-73AA-491A-BE95-2126CAAAEAD5}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AJ29"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
@@ -53194,7 +53198,7 @@
     <col min="6" max="6" width="29.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="44.77734375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="255.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" customWidth="1"/>
     <col min="10" max="10" width="8.44140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="24.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="44.77734375" bestFit="1" customWidth="1"/>
@@ -53548,7 +53552,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>35</v>
       </c>
@@ -54098,7 +54102,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>35</v>
       </c>
@@ -54535,7 +54539,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -54856,7 +54860,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -55070,7 +55074,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -55275,7 +55279,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -55385,7 +55389,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -55495,7 +55499,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -55605,7 +55609,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>35</v>
       </c>
@@ -55715,7 +55719,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>35</v>
       </c>
@@ -55825,7 +55829,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>35</v>
       </c>
@@ -56244,7 +56248,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>1210</v>
       </c>
@@ -56337,6 +56341,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AJ29" xr:uid="{37091296-73AA-491A-BE95-2126CAAAEAD5}">
+    <filterColumn colId="26">
+      <customFilters>
+        <customFilter operator="greaterThanOrEqual" val="20"/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -56345,6 +56356,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3FD05B9-2A3A-4661-BFE6-86B4B4D2B6EA}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AJ9"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
@@ -57300,6 +57312,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AJ9" xr:uid="{B3FD05B9-2A3A-4661-BFE6-86B4B4D2B6EA}">
+    <filterColumn colId="26">
+      <customFilters>
+        <customFilter operator="greaterThanOrEqual" val="20"/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -57308,6 +57327,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49B70CA9-6985-4D07-8082-4316A240EBD2}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AJ219"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
@@ -57427,7 +57447,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>35</v>
       </c>
@@ -57534,7 +57554,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -58283,7 +58303,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>35</v>
       </c>
@@ -58720,7 +58740,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -58830,7 +58850,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -58940,7 +58960,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -62442,7 +62462,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="48" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>35</v>
       </c>
@@ -64731,7 +64751,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="69" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>35</v>
       </c>
@@ -65382,7 +65402,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="75" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>35</v>
       </c>
@@ -65593,7 +65613,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="77" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>35</v>
       </c>
@@ -66128,7 +66148,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="82" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>35</v>
       </c>
@@ -66675,7 +66695,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="87" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>35</v>
       </c>
@@ -67635,7 +67655,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="96" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>35</v>
       </c>
@@ -67745,7 +67765,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="97" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>35</v>
       </c>
@@ -68289,7 +68309,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="102" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>35</v>
       </c>
@@ -68393,7 +68413,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="103" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>35</v>
       </c>
@@ -68595,7 +68615,7 @@
         <v>2407</v>
       </c>
     </row>
-    <row r="105" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>35</v>
       </c>
@@ -68699,7 +68719,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="106" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>35</v>
       </c>
@@ -68809,7 +68829,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="107" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>35</v>
       </c>
@@ -69133,7 +69153,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="110" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>35</v>
       </c>
@@ -69772,7 +69792,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="116" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>35</v>
       </c>
@@ -69882,7 +69902,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="117" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>35</v>
       </c>
@@ -69992,7 +70012,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="118" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>35</v>
       </c>
@@ -70102,7 +70122,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="119" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>35</v>
       </c>
@@ -70212,7 +70232,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="120" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>35</v>
       </c>
@@ -70322,7 +70342,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="121" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>35</v>
       </c>
@@ -70432,7 +70452,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="122" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>35</v>
       </c>
@@ -70542,7 +70562,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="123" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>35</v>
       </c>
@@ -70652,7 +70672,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="124" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>35</v>
       </c>
@@ -70762,7 +70782,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="125" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>35</v>
       </c>
@@ -70872,7 +70892,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="126" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>35</v>
       </c>
@@ -70982,7 +71002,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="127" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>35</v>
       </c>
@@ -71092,7 +71112,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="128" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>35</v>
       </c>
@@ -71202,7 +71222,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="129" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>35</v>
       </c>
@@ -71312,7 +71332,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="130" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>35</v>
       </c>
@@ -71422,7 +71442,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="131" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>35</v>
       </c>
@@ -71532,7 +71552,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="132" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>35</v>
       </c>
@@ -71642,7 +71662,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="133" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>35</v>
       </c>
@@ -71752,7 +71772,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="134" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>35</v>
       </c>
@@ -71862,7 +71882,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="135" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>35</v>
       </c>
@@ -71972,7 +71992,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="136" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>35</v>
       </c>
@@ -72082,7 +72102,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="137" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>35</v>
       </c>
@@ -72192,7 +72212,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="138" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>35</v>
       </c>
@@ -72302,7 +72322,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="139" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>35</v>
       </c>
@@ -72412,7 +72432,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="140" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>35</v>
       </c>
@@ -73054,7 +73074,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="146" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>35</v>
       </c>
@@ -74733,7 +74753,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="162" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>35</v>
       </c>
@@ -74950,7 +74970,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="164" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>35</v>
       </c>
@@ -75167,7 +75187,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="166" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>35</v>
       </c>
@@ -76576,7 +76596,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="179" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>35</v>
       </c>
@@ -76790,7 +76810,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="181" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>35</v>
       </c>
@@ -76897,7 +76917,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="182" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>35</v>
       </c>
@@ -77108,7 +77128,7 @@
         <v>2869</v>
       </c>
     </row>
-    <row r="184" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>35</v>
       </c>
@@ -77800,7 +77820,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="191" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>1210</v>
       </c>
@@ -79644,7 +79664,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="210" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:34" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>1210</v>
       </c>
@@ -79742,7 +79762,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="211" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:34" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>1210</v>
       </c>
@@ -79840,7 +79860,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="212" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:34" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>1210</v>
       </c>
@@ -79938,7 +79958,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="213" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:34" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>1210</v>
       </c>
@@ -80613,6 +80633,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AJ219" xr:uid="{49B70CA9-6985-4D07-8082-4316A240EBD2}">
+    <filterColumn colId="26">
+      <customFilters>
+        <customFilter operator="greaterThanOrEqual" val="20"/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
